--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
   <si>
     <t>Filename</t>
   </si>
@@ -808,700 +808,697 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9951,0.0005,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.9869,0.0002,0.0001,0.0116</t>
-  </si>
-  <si>
-    <t>0.0200,0.0007,0.0004,0.9875</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9538,0.0001,0.0002,0.0546</t>
+  </si>
+  <si>
+    <t>0.0120,0.0006,0.0006,0.9929</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9914,0.0006,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0771,0.0021,0.9093,0.0010</t>
+  </si>
+  <si>
+    <t>0.0298,0.0004,0.9853,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.0005,0.9959,0.0002</t>
+  </si>
+  <si>
+    <t>0.9943,0.0006,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9957,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.1539,0.8664,0.0070,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.9975,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4541,0.0019,0.4769,0.0011</t>
+  </si>
+  <si>
+    <t>0.5311,0.0008,0.4595,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0275,0.0006,0.9822,0.0001</t>
+  </si>
+  <si>
+    <t>0.0052,0.0001,0.9959,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0002,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9985,0.0003</t>
+  </si>
+  <si>
+    <t>0.0032,0.9950,0.0007,0.0028</t>
+  </si>
+  <si>
+    <t>0.9892,0.0031,0.0026,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.0637,0.2005,0.4979,0.0001</t>
+  </si>
+  <si>
+    <t>0.9845,0.0078,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9796,0.0007,0.0079,0.0002</t>
+  </si>
+  <si>
+    <t>0.3061,0.6996,0.0036,0.0012</t>
+  </si>
+  <si>
+    <t>0.0039,0.9877,0.0154,0.0013</t>
+  </si>
+  <si>
+    <t>0.0084,0.0863,0.8735,0.0039</t>
+  </si>
+  <si>
+    <t>0.0029,0.0004,0.9910,0.0019</t>
+  </si>
+  <si>
+    <t>0.0026,0.0012,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.0628,0.0002,0.9683,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.0072,0.9876,0.0005</t>
+  </si>
+  <si>
+    <t>0.0034,0.9823,0.0237,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.9090,0.0007,0.9682</t>
+  </si>
+  <si>
+    <t>0.0008,0.9949,0.0033,0.0035</t>
+  </si>
+  <si>
+    <t>0.0002,0.9980,0.0119,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0103,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0064,0.0002,0.9928,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0027,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0011,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9810,0.0229,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0025,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0037,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9604,0.9885,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0017,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0009,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9907,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9984,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9986,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9789,0.0023,0.0086,0.0003</t>
+  </si>
+  <si>
+    <t>0.8385,0.0049,0.1034,0.0017</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9992,0.0042</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9258,0.9563,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9967,0.1462,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9339,0.0000</t>
+  </si>
+  <si>
+    <t>0.1624,0.0000,0.0050,0.7817</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0007,0.9993</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0010,0.9993</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9879,0.7744,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9798,0.9451,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.6523,0.9935,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.5351,0.9921,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9916,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9524,0.9721,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9200,0.0021,0.0559,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0005,0.9958,0.0021</t>
-  </si>
-  <si>
-    <t>0.3845,0.0000,0.8654,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0005,0.9969,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0004,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.3257,0.6643,0.0191,0.0011</t>
-  </si>
-  <si>
-    <t>0.0085,0.9913,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8608,0.0002,0.1536,0.0003</t>
-  </si>
-  <si>
-    <t>0.3106,0.0008,0.6810,0.0010</t>
-  </si>
-  <si>
-    <t>0.0010,0.0011,0.9965,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0358,0.0007,0.9678,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0002,0.9970,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0007</t>
-  </si>
-  <si>
-    <t>0.0125,0.9827,0.0009,0.0067</t>
-  </si>
-  <si>
-    <t>0.9971,0.0012,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9998,0.0025</t>
-  </si>
-  <si>
-    <t>0.0165,0.9455,0.0299,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0005,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9221,0.0018,0.0272,0.0008</t>
-  </si>
-  <si>
-    <t>0.6770,0.3529,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.0028,0.9933,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0037,0.9958,0.0013</t>
-  </si>
-  <si>
-    <t>0.0048,0.0010,0.9850,0.0025</t>
-  </si>
-  <si>
-    <t>0.0208,0.0009,0.9698,0.0009</t>
-  </si>
-  <si>
-    <t>0.0035,0.0009,0.9929,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.0027,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.8446,0.0007,0.9336</t>
-  </si>
-  <si>
-    <t>0.0006,0.9981,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9989,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.1895,0.9968,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9987,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0018,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0021,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9777,0.0009,0.0090,0.0006</t>
-  </si>
-  <si>
-    <t>0.9746,0.0101,0.0057,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0014,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0020,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9838,0.9106,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0007,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0043,0.9968,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.9959,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9984,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9917,0.0002,0.0054,0.0000</t>
-  </si>
-  <si>
-    <t>0.8322,0.0056,0.0735,0.0045</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9992,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9955,0.5047,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9968,0.0228,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9322,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0710,0.9945</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0004,0.9995</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.9965,0.0206,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9950,0.9936,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.6013,0.9871,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8369,0.9735,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9788,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9719,0.7137,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0028,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
+    <t>0.9976,0.0022,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.0159,0.9935,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0001,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0169,0.0001,0.9908,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9984,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9975,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0070,0.9937,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9975,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9980,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.3166,0.6697,0.0316,0.0011</t>
+  </si>
+  <si>
+    <t>0.0905,0.0048,0.8200,0.0057</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.1821,0.1857,0.0785,0.0081</t>
+  </si>
+  <si>
+    <t>0.0676,0.0065,0.8936,0.0027</t>
+  </si>
+  <si>
+    <t>0.0001,0.9550,0.0005,0.9368</t>
+  </si>
+  <si>
+    <t>0.0020,0.9825,0.0968,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9884,0.9848,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8593,0.1704,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9081,0.1006,0.0038,0.0022</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.0040,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.9759,0.0004,0.0130,0.0004</t>
-  </si>
-  <si>
-    <t>0.0013,0.0002,0.9980,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.9959,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.9972,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.9959,0.0104,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.9988,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.4129,0.6815,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.4305,0.0039,0.4403,0.0016</t>
-  </si>
-  <si>
-    <t>0.9931,0.0018,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0167,0.0029,0.6861,0.1923</t>
-  </si>
-  <si>
-    <t>0.0109,0.0008,0.9867,0.0009</t>
-  </si>
-  <si>
-    <t>0.0049,0.7069,0.0058,0.8279</t>
-  </si>
-  <si>
-    <t>0.0017,0.9974,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9647,0.9839,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.4124,0.6333,0.0060,0.0011</t>
-  </si>
-  <si>
-    <t>0.8725,0.1381,0.0024,0.0021</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.4267,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9306,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0047,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0028,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.9955,0.0001,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0399,0.0003,0.9658,0.0012</t>
-  </si>
-  <si>
-    <t>0.0666,0.0001,0.9713,0.0001</t>
-  </si>
-  <si>
-    <t>0.9447,0.0007,0.0438,0.0006</t>
-  </si>
-  <si>
-    <t>0.1346,0.0004,0.0001,0.9652</t>
+    <t>0.9984,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0386,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.8046,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0113,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0616,0.0030,0.9444,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0001,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.6165,0.0193,0.1866,0.0057</t>
+  </si>
+  <si>
+    <t>0.0106,0.0001,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.9921,0.0003,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.3581,0.0001,0.0002,0.8753</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9970,0.9930,0.0000</t>
-  </si>
-  <si>
-    <t>0.0592,0.9378,0.0014,0.0024</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0569,0.9496,0.0046,0.0005</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.1276,0.0001,0.0020,0.9221</t>
-  </si>
-  <si>
-    <t>0.9986,0.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0019,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.9864,0.0000,0.0040,0.0006</t>
-  </si>
-  <si>
-    <t>0.9956,0.0000,0.0000,0.0066</t>
-  </si>
-  <si>
-    <t>0.2926,0.0853,0.1884,0.0024</t>
-  </si>
-  <si>
-    <t>0.9958,0.0018,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9701,0.0194,0.0016,0.0011</t>
-  </si>
-  <si>
-    <t>0.0612,0.8983,0.0095,0.0031</t>
-  </si>
-  <si>
-    <t>0.6855,0.0119,0.2304,0.0021</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0007,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9978,0.0007,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9524,0.0644,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9267,0.0781,0.0041,0.0005</t>
-  </si>
-  <si>
-    <t>0.5795,0.5175,0.0048,0.0003</t>
-  </si>
-  <si>
-    <t>0.1775,0.1515,0.7048,0.0033</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0016,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9981,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9701,0.0269,0.0018,0.0018</t>
-  </si>
-  <si>
-    <t>0.0001,0.0046,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9608,0.0112,0.0134,0.0109</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0038,0.9981,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.0030,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0034,0.0033,0.9878,0.0014</t>
-  </si>
-  <si>
-    <t>0.0613,0.0002,0.9760,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0006,0.9954,0.0003</t>
-  </si>
-  <si>
-    <t>0.0041,0.0038,0.9901,0.0005</t>
-  </si>
-  <si>
-    <t>0.0480,0.0080,0.8933,0.0009</t>
-  </si>
-  <si>
-    <t>0.0153,0.0012,0.9834,0.0005</t>
-  </si>
-  <si>
-    <t>0.9736,0.0103,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.3287,0.0196,0.6305,0.0012</t>
-  </si>
-  <si>
-    <t>0.0015,0.9980,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.9976,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.7143,0.4287,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2150,0.8346,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.0156,0.9884,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.5968,0.0437,0.1624,0.0011</t>
-  </si>
-  <si>
-    <t>0.9779,0.0019,0.0088,0.0002</t>
-  </si>
-  <si>
-    <t>0.9779,0.0020,0.0029,0.0030</t>
-  </si>
-  <si>
-    <t>0.8699,0.0071,0.0560,0.0036</t>
-  </si>
-  <si>
-    <t>0.6449,0.0016,0.2483,0.0011</t>
-  </si>
-  <si>
-    <t>0.0019,0.0009,0.9950,0.0027</t>
-  </si>
-  <si>
-    <t>0.0018,0.0087,0.9921,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0829,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0020,0.9945,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0672,0.9924,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0014,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9932,0.0049,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9958,0.0027,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9961,0.0022,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9970,0.0003,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0029,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0829,0.1228,0.6716,0.0040</t>
-  </si>
-  <si>
-    <t>0.9631,0.0010,0.0127,0.0008</t>
-  </si>
-  <si>
-    <t>0.0012,0.0003,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9995,0.0005</t>
-  </si>
-  <si>
-    <t>0.0007,0.1371,0.9935,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0015,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0011,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0012,0.9932,0.0011</t>
-  </si>
-  <si>
-    <t>0.7994,0.0005,0.0986,0.0052</t>
-  </si>
-  <si>
-    <t>0.7804,0.0002,0.2417,0.0004</t>
-  </si>
-  <si>
-    <t>0.9605,0.0006,0.0260,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
+    <t>0.0000,0.9910,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.1636,0.8399,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.2790,0.7340,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0300,0.0000,0.0005,0.9857</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0046,0.9967,0.0007</t>
+  </si>
+  <si>
+    <t>0.9969,0.0001,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.1911,0.0875,0.2947,0.0058</t>
+  </si>
+  <si>
+    <t>0.9981,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9840,0.0097,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.0826,0.8781,0.0088,0.0024</t>
+  </si>
+  <si>
+    <t>0.9289,0.0412,0.0017,0.0025</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9765,0.0312,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.8823,0.1153,0.0073,0.0004</t>
+  </si>
+  <si>
+    <t>0.4628,0.6460,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0125,0.6556,0.7964,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0014,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9958,0.0013,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9619,0.0292,0.0040,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.0065,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6810,0.0778,0.2625,0.0401</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0011,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0000,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0036,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0251,0.0041,0.9564,0.0008</t>
+  </si>
+  <si>
+    <t>0.0326,0.0006,0.9799,0.0002</t>
+  </si>
+  <si>
+    <t>0.5400,0.0040,0.4059,0.0010</t>
+  </si>
+  <si>
+    <t>0.0012,0.0411,0.9915,0.0002</t>
+  </si>
+  <si>
+    <t>0.0374,0.0132,0.9163,0.0006</t>
+  </si>
+  <si>
+    <t>0.9240,0.0082,0.0291,0.0008</t>
+  </si>
+  <si>
+    <t>0.2883,0.0014,0.5654,0.0069</t>
+  </si>
+  <si>
+    <t>0.1257,0.0131,0.8595,0.0003</t>
+  </si>
+  <si>
+    <t>0.0031,0.9960,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.9977,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9684,0.0466,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.5792,0.5504,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0429,0.9656,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9754,0.0048,0.0054,0.0006</t>
+  </si>
+  <si>
+    <t>0.8970,0.0002,0.1333,0.0001</t>
+  </si>
+  <si>
+    <t>0.9763,0.0009,0.0006,0.0071</t>
+  </si>
+  <si>
+    <t>0.8833,0.0112,0.0469,0.0041</t>
+  </si>
+  <si>
+    <t>0.9893,0.0008,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0005,0.9958,0.0225</t>
+  </si>
+  <si>
+    <t>0.0007,0.0035,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0131,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.0293,0.0010,0.9756,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.2894,0.9266,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0040,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0027,0.0002,0.0003</t>
   </si>
   <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0028,0.9961,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0231,0.9996,0.0000</t>
+    <t>0.9981,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0124,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0123,0.0329,0.9098,0.0045</t>
+  </si>
+  <si>
+    <t>0.3762,0.0008,0.5093,0.0034</t>
+  </si>
+  <si>
+    <t>0.0017,0.0003,0.9968,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0040,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.1787,0.9939,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0010,0.0037,0.9960,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0095,0.0006,0.9823,0.0058</t>
-  </si>
-  <si>
-    <t>0.0156,0.0002,0.9878,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0005,0.9964,0.0012</t>
-  </si>
-  <si>
-    <t>0.9045,0.0012,0.0199,0.0158</t>
-  </si>
-  <si>
-    <t>0.0071,0.0044,0.0000,0.9975</t>
-  </si>
-  <si>
-    <t>0.0049,0.0002,0.0007,0.9967</t>
-  </si>
-  <si>
-    <t>0.9954,0.0003,0.0002,0.0020</t>
+    <t>0.0089,0.0023,0.9856,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9982,0.0004</t>
+  </si>
+  <si>
+    <t>0.0017,0.0009,0.9947,0.0020</t>
+  </si>
+  <si>
+    <t>0.5307,0.0003,0.5446,0.0003</t>
+  </si>
+  <si>
+    <t>0.2592,0.0001,0.8411,0.0005</t>
+  </si>
+  <si>
+    <t>0.9942,0.0004,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9838,0.0143,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.9989,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9820,0.0316,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0123,0.1021,0.8745,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0027,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0170,0.9913,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0664,0.0009,0.8820,0.0119</t>
+  </si>
+  <si>
+    <t>0.0029,0.0007,0.9948,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0007,0.9977,0.0008</t>
+  </si>
+  <si>
+    <t>0.8735,0.0001,0.0026,0.0586</t>
+  </si>
+  <si>
+    <t>0.0011,0.0223,0.0000,0.9991</t>
+  </si>
+  <si>
+    <t>0.0073,0.0002,0.0002,0.9969</t>
+  </si>
+  <si>
+    <t>0.9934,0.0013,0.0005,0.0022</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1884,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1901,7 +1898,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1915,7 +1912,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1929,7 +1926,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1943,7 +1940,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1957,7 +1954,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1971,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1999,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2013,7 +2010,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2027,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2041,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2055,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2069,7 +2066,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2083,7 +2080,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2097,7 +2094,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2111,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2125,7 +2122,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2139,7 +2136,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2153,7 +2150,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2167,7 +2164,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2181,7 +2178,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2192,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2206,10 +2203,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2223,7 +2220,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2237,7 +2234,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2251,7 +2248,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2265,7 +2262,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2279,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2293,7 +2290,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2307,7 +2304,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2321,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2332,10 +2329,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2349,7 +2346,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2363,7 +2360,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2391,7 +2388,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2405,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2419,7 +2416,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2433,7 +2430,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2447,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2461,7 +2458,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2475,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2489,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2500,10 +2497,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2517,7 +2514,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2531,7 +2528,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2545,7 +2542,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2559,7 +2556,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2573,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2587,7 +2584,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2601,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2615,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2629,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2643,7 +2640,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2657,7 +2654,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2671,7 +2668,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2685,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2699,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2713,7 +2710,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2727,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2741,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2755,7 +2752,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2769,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2783,7 +2780,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2797,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2811,7 +2808,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2825,7 +2822,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2839,7 +2836,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2853,7 +2850,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2867,7 +2864,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2881,7 +2878,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2895,7 +2892,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2909,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2923,7 +2920,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2937,7 +2934,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2951,7 +2948,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2965,7 +2962,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2979,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2993,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3007,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3018,10 +3015,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3035,7 +3032,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3049,7 +3046,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3063,7 +3060,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3077,7 +3074,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3091,7 +3088,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3105,7 +3102,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3119,7 +3116,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3133,7 +3130,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3147,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3161,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3175,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3189,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3203,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3231,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>359</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3259,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3273,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3287,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3301,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3329,7 +3326,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3343,7 +3340,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3357,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3371,7 +3368,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3385,7 +3382,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3399,7 +3396,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3413,7 +3410,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3427,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3441,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3455,7 +3452,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3469,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3480,10 +3477,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3497,7 +3494,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3508,10 +3505,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3525,7 +3522,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3536,10 +3533,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3553,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3567,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3581,7 +3578,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3595,7 +3592,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3609,7 +3606,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3620,10 +3617,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3637,7 +3634,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3651,7 +3648,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>380</v>
+        <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3665,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3679,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3693,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>269</v>
+        <v>386</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3707,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3721,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3735,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3749,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3763,7 +3760,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3777,7 +3774,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3791,7 +3788,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3805,7 +3802,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3819,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3830,10 +3827,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3847,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3861,7 +3858,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3875,7 +3872,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3889,7 +3886,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3903,7 +3900,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3917,7 +3914,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3931,7 +3928,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3945,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3959,7 +3956,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3973,7 +3970,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3987,7 +3984,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4001,7 +3998,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4015,7 +4012,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4029,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4043,7 +4040,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4057,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4071,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4082,10 +4079,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4099,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4113,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4127,7 +4124,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4141,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4155,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4169,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4183,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>413</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4197,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4211,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>415</v>
+        <v>354</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4225,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>353</v>
+        <v>274</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4239,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>354</v>
+        <v>416</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4253,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4267,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>417</v>
+        <v>354</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4320,7 +4317,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
         <v>421</v>
@@ -4544,7 +4541,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
         <v>437</v>
@@ -4586,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
         <v>440</v>
@@ -4600,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>441</v>
@@ -4670,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D201" t="s">
         <v>446</v>
@@ -4841,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>353</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4855,7 +4852,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4869,7 +4866,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4883,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4897,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4911,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>380</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4925,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4939,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4953,7 +4950,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4967,7 +4964,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4978,10 +4975,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4995,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5009,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5023,7 +5020,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5037,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5051,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5065,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5079,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5093,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5104,10 +5101,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5118,10 +5115,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5135,7 +5132,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5149,7 +5146,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5163,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>277</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5177,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5191,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5205,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>480</v>
+        <v>277</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5219,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>356</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5233,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5247,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5261,7 +5258,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5275,7 +5272,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5289,7 +5286,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5303,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5317,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5331,7 +5328,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5345,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5359,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5373,7 +5370,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5387,7 +5384,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5401,7 +5398,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5415,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5429,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5443,7 +5440,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
